--- a/rbda-kiosk/du_lieu_test/TEST_04_CO_LOI_CO_Y.xlsx
+++ b/rbda-kiosk/du_lieu_test/TEST_04_CO_LOI_CO_Y.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -439,6 +439,7 @@
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -467,6 +468,11 @@
           <t>pref_2</t>
         </is>
       </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>score_1</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -490,6 +496,7 @@
           <t>clb_amnhac</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,6 +516,7 @@
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -528,6 +536,7 @@
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -547,6 +556,7 @@
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -570,6 +580,7 @@
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -589,6 +600,7 @@
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -608,6 +620,9 @@
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
+      <c r="F8" t="n">
+        <v>8.5</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -627,6 +642,7 @@
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -646,6 +662,7 @@
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -665,6 +682,7 @@
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -677,7 +695,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A27"/>
+  <dimension ref="A1:A31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="82" customWidth="1" min="1" max="1"/>
@@ -713,7 +731,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Năm lỗi đã cài sẵn, và cảnh báo tương ứng phải hiện ra:</t>
+          <t>Sáu lỗi đã cài sẵn, và cảnh báo tương ứng phải hiện ra:</t>
         </is>
       </c>
     </row>
@@ -808,29 +826,53 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Nếu thiếu bất kỳ cảnh báo nào trong 5 cảnh báo trên, đó là lỗi</t>
+          <t>6. File này có cột score_1, nhưng đây là file NGUYỆN VỌNG —</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>của phần mềm — hãy báo lại.</t>
+          <t xml:space="preserve">   điểm chỉ nạp được từ file chọn CLB muốn thi</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   -&gt; báo: điểm trong file này KHÔNG được nạp</t>
+        </is>
+      </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Sinh bằng du_lieu_test/tao_du_lieu_test.py, seed = 2026</t>
-        </is>
-      </c>
+      <c r="A26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
+        <is>
+          <t>Nếu thiếu bất kỳ cảnh báo nào trong 6 cảnh báo trên, đó là lỗi</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>của phần mềm — hãy báo lại.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Sinh bằng du_lieu_test/tao_du_lieu_test.py, seed = 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
         <is>
           <t>Chạy lại script luôn cho ra đúng bộ dữ liệu này.</t>
         </is>
